--- a/LED_MUX_CONTROLLER_testplan.xlsx
+++ b/LED_MUX_CONTROLLER_testplan.xlsx
@@ -551,7 +551,7 @@
     <col width="22" customWidth="1" style="13" min="7" max="7"/>
     <col width="16" customWidth="1" style="13" min="8" max="8"/>
     <col width="34" customWidth="1" style="13" min="9" max="9"/>
-    <col width="10.12" customWidth="1" style="12" min="10" max="10"/>
+    <col width="10" customWidth="1" style="12" min="10" max="10"/>
     <col width="10.86" customWidth="1" style="12" min="11" max="11"/>
     <col width="7.07" customWidth="1" style="12" min="12" max="12"/>
     <col width="5.28" customWidth="1" style="12" min="13" max="13"/>
@@ -603,6 +603,11 @@
           <t>Tests</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
       <c r="AMJ1" s="12" t="n"/>
     </row>
     <row r="2" ht="48.75" customHeight="1" s="17">
@@ -655,6 +660,11 @@
           <t>led_reset_values_test</t>
         </is>
       </c>
+      <c r="J3" s="18" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="23.25" customHeight="1" s="17">
       <c r="A4" s="18" t="inlineStr"/>
@@ -699,6 +709,11 @@
           <t>apb_reset_defaults_test</t>
         </is>
       </c>
+      <c r="J4" s="18" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="12.85" customHeight="1" s="17">
       <c r="A5" s="18" t="inlineStr"/>
@@ -739,6 +754,11 @@
           <t>apb_led_enable_write_read_test</t>
         </is>
       </c>
+      <c r="J5" s="18" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="12.85" customHeight="1" s="17">
       <c r="A6" s="18" t="inlineStr"/>
@@ -773,6 +793,11 @@
           <t>apb_scratchpad_wr_rd_test</t>
         </is>
       </c>
+      <c r="J6" s="18" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="25.5" customHeight="1" s="17">
       <c r="A7" s="18" t="inlineStr"/>
@@ -791,15 +816,11 @@
         <is>
           <t>1) Write 0x4004=32'hFFFF_FFFF.
 2) Read 0x4004.
-Constraints: Done is RO; writes have no effect (C-7, FR 3.5).
-Checkers: SCB-2; MON attempted RO write.</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>attempted RO write</t>
-        </is>
-      </c>
+Constraints: Done is RO; sequence drives the illegal write (C-7, FR 3.5).
+Checkers: SCB-2.</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr"/>
       <c r="G7" s="18" t="inlineStr"/>
       <c r="H7" s="18" t="inlineStr">
         <is>
@@ -809,6 +830,11 @@
       <c r="I7" s="18" t="inlineStr">
         <is>
           <t>apb_done_read_only_test</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -847,6 +873,11 @@
       <c r="I8" s="18" t="inlineStr">
         <is>
           <t>apb_pready_no_wait_test</t>
+        </is>
+      </c>
+      <c r="J8" s="18" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
     </row>
@@ -889,6 +920,11 @@
           <t>apb_default_enable_led_path_test</t>
         </is>
       </c>
+      <c r="J9" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="12.8" customHeight="1" s="17">
       <c r="A10" s="18" t="inlineStr"/>
@@ -914,12 +950,12 @@
 3) Read 0x0000.
 4) Check pslerr.
 Constraints: addr NOT IN {0x4000, 0x4004, 0x4008} (AC-A2).
-Checkers: assert_apb_pslerr_invalid_addr; MON pslerr==1.</t>
+Checkers: assert_apb_pslerr_invalid_addr.</t>
         </is>
       </c>
       <c r="F10" s="18" t="inlineStr">
         <is>
-          <t>assert_apb_pslerr_invalid_addr, pslerr==1</t>
+          <t>assert_apb_pslerr_invalid_addr</t>
         </is>
       </c>
       <c r="G10" s="18" t="inlineStr"/>
@@ -931,6 +967,11 @@
       <c r="I10" s="18" t="inlineStr">
         <is>
           <t>apb_invalid_addr_test</t>
+        </is>
+      </c>
+      <c r="J10" s="18" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
     </row>
@@ -967,6 +1008,11 @@
           <t>apb_done_poll_timeout_test</t>
         </is>
       </c>
+      <c r="J11" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="12.8" customHeight="1" s="17">
       <c r="A12" s="18" t="inlineStr"/>
@@ -1001,6 +1047,11 @@
           <t>apb_scratchpad_all_ones_test</t>
         </is>
       </c>
+      <c r="J12" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="12.8" customHeight="1" s="17">
       <c r="A13" s="18" t="inlineStr"/>
@@ -1032,6 +1083,11 @@
       <c r="I13" s="18" t="inlineStr">
         <is>
           <t>apb_scratchpad_walking_one_test</t>
+        </is>
+      </c>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -1073,6 +1129,11 @@
           <t>apb_enable_toggle_stress_test</t>
         </is>
       </c>
+      <c r="J14" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="18" t="inlineStr"/>
@@ -1110,6 +1171,11 @@
       <c r="I15" s="18" t="inlineStr">
         <is>
           <t>apb_read_during_processing_test</t>
+        </is>
+      </c>
+      <c r="J15" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
     </row>
@@ -1156,6 +1222,11 @@
           <t>led_single_digit_zero_test</t>
         </is>
       </c>
+      <c r="J16" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="18" t="inlineStr"/>
@@ -1196,6 +1267,11 @@
           <t>led_single_digit_one_test</t>
         </is>
       </c>
+      <c r="J17" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="18" t="inlineStr"/>
@@ -1240,6 +1316,11 @@
           <t>led_decimal_42_test</t>
         </is>
       </c>
+      <c r="J18" s="18" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="18" t="inlineStr"/>
@@ -1283,6 +1364,11 @@
           <t>led_max_displayable_test</t>
         </is>
       </c>
+      <c r="J19" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="18" t="inlineStr"/>
@@ -1301,14 +1387,14 @@
         <is>
           <t>1) Drive error_q=74565.
 2) Hold &gt;=1002 cycles.
-3) Monitor samples sel_out one-hot.
+3) Collect 6+ sel_out samples.
 Constraints: Hold 1002 cycles (C-4, AC-M1, AC-M2).
-Checkers: SCB-5; assert_sel_out_onehot_active_low, cover_sel_out_digit_position; MON one-hot; COV cg_digits.</t>
+Checkers: SCB-5; assert_sel_out_onehot_active_low, cover_sel_out_digit_position; COV cg_digits.</t>
         </is>
       </c>
       <c r="F20" s="18" t="inlineStr">
         <is>
-          <t>assert_sel_out_onehot_active_low, cover_sel_out_digit_position, one-hot</t>
+          <t>assert_sel_out_onehot_active_low, cover_sel_out_digit_position</t>
         </is>
       </c>
       <c r="G20" s="18" t="inlineStr">
@@ -1324,6 +1410,11 @@
       <c r="I20" s="18" t="inlineStr">
         <is>
           <t>led_sel_onehot_scan_test</t>
+        </is>
+      </c>
+      <c r="J20" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
     </row>
@@ -1365,6 +1456,11 @@
           <t>led_seg_active_low_test</t>
         </is>
       </c>
+      <c r="J21" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="18" t="inlineStr"/>
@@ -1384,13 +1480,13 @@
           <t>1) Drive error_q.
 2) Hold exactly 1002 cycles.
 3) Poll Done.
-Constraints: Hold error_q for 1002 cycles (C-4, AC-M2).
-Checkers: check_hold_1002_cycle; MON hold enforced; SCB-4.</t>
+Constraints: Hold error_q for 1002 cycles; sequence enforces hold duration (C-4, AC-M2).
+Checkers: check_hold_1002_cycle; SCB-4.</t>
         </is>
       </c>
       <c r="F22" s="18" t="inlineStr">
         <is>
-          <t>check_hold_1002_cycle, hold enforced</t>
+          <t>check_hold_1002_cycle</t>
         </is>
       </c>
       <c r="G22" s="18" t="inlineStr"/>
@@ -1402,6 +1498,11 @@
       <c r="I22" s="18" t="inlineStr">
         <is>
           <t>led_hold_time_min_test</t>
+        </is>
+      </c>
+      <c r="J22" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
     </row>
@@ -1423,13 +1524,13 @@
           <t>1) Drive error_q=100.
 2) Wait 60-80 cycles.
 3) Sample outputs.
-Constraints: Do not sample before 60 cycles (C-5, AC-E1).
-Checkers: check_60_80_cycle; MON defer sampling; SCB-8.</t>
+Constraints: Sequence waits &gt;=60 cycles before sampling (C-5, AC-E1).
+Checkers: check_60_80_cycle; SCB-8.</t>
         </is>
       </c>
       <c r="F23" s="18" t="inlineStr">
         <is>
-          <t>check_60_80_cycle, defer sampling</t>
+          <t>check_60_80_cycle</t>
         </is>
       </c>
       <c r="G23" s="18" t="inlineStr"/>
@@ -1441,6 +1542,11 @@
       <c r="I23" s="18" t="inlineStr">
         <is>
           <t>led_latency_window_test</t>
+        </is>
+      </c>
+      <c r="J23" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
     </row>
@@ -1490,6 +1596,11 @@
           <t>led_overflow_modulo_test</t>
         </is>
       </c>
+      <c r="J24" s="18" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="18" t="inlineStr"/>
@@ -1529,6 +1640,11 @@
           <t>led_overflow_max_test</t>
         </is>
       </c>
+      <c r="J25" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="18" t="inlineStr"/>
@@ -1564,6 +1680,11 @@
       <c r="I26" s="18" t="inlineStr">
         <is>
           <t>led_overflow_boundary_test</t>
+        </is>
+      </c>
+      <c r="J26" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -1603,6 +1724,11 @@
       <c r="I27" s="18" t="inlineStr">
         <is>
           <t>led_disable_blocks_update_test</t>
+        </is>
+      </c>
+      <c r="J27" s="18" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
     </row>
@@ -1642,6 +1768,11 @@
           <t>led_reenable_after_disable_test</t>
         </is>
       </c>
+      <c r="J28" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="18" t="inlineStr"/>
@@ -1661,15 +1792,11 @@
           <t>1) Drive error_q=10, hold.
 2) Drive error_q=99, hold.
 3) Poll Done after each.
-Constraints: Hold &gt;=1002 each (C-4, C-5).
-Checkers: SCB-4; MON latency restarts.</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>latency restarts</t>
-        </is>
-      </c>
+Constraints: Hold &gt;=1002 each; sequence restarts hold per error_q change (C-4, C-5).
+Checkers: SCB-4.</t>
+        </is>
+      </c>
+      <c r="F29" s="18" t="inlineStr"/>
       <c r="G29" s="18" t="inlineStr"/>
       <c r="H29" s="18" t="inlineStr">
         <is>
@@ -1679,6 +1806,11 @@
       <c r="I29" s="18" t="inlineStr">
         <is>
           <t>led_back_to_back_error_test</t>
+        </is>
+      </c>
+      <c r="J29" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -1721,6 +1853,11 @@
           <t>led_reset_during_display_test</t>
         </is>
       </c>
+      <c r="J30" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="35.35" customFormat="1" customHeight="1" s="13">
       <c r="A31" s="18" t="inlineStr"/>
@@ -1756,6 +1893,11 @@
           <t>led_done_clear_after_reset_test</t>
         </is>
       </c>
+      <c r="J31" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="48.75" customHeight="1" s="17">
       <c r="A32" s="18" t="inlineStr"/>
@@ -1774,15 +1916,11 @@
         <is>
           <t>1) Hold error_q for 1000 cycles (&lt; C-4 min).
 2) Drive error_q.
-Constraints: Hold 1000 cycles violates C-4.
-Checkers: MON/test expect failure or Done!=1.</t>
-        </is>
-      </c>
-      <c r="F32" s="18" t="inlineStr">
-        <is>
-          <t>/test expect failure or Done!=1</t>
-        </is>
-      </c>
+Constraints: Hold 1000 cycles violates C-4; sequence drives short hold.
+Checkers: SCB-8; test expect failure or DUT not Done.</t>
+        </is>
+      </c>
+      <c r="F32" s="18" t="inlineStr"/>
       <c r="G32" s="18" t="inlineStr"/>
       <c r="H32" s="18" t="inlineStr">
         <is>
@@ -1792,6 +1930,11 @@
       <c r="I32" s="18" t="inlineStr">
         <is>
           <t>led_hold_below_min_negative_test</t>
+        </is>
+      </c>
+      <c r="J32" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -1833,6 +1976,11 @@
       <c r="I33" s="18" t="inlineStr">
         <is>
           <t>led_all_digits_0_to_9_test</t>
+        </is>
+      </c>
+      <c r="J33" s="18" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
     </row>
@@ -1884,6 +2032,11 @@
           <t>smoke_test</t>
         </is>
       </c>
+      <c r="J34" s="18" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="12.85" customHeight="1" s="17">
       <c r="A35" s="18" t="inlineStr"/>
@@ -1921,6 +2074,11 @@
           <t>full_display_flow_test</t>
         </is>
       </c>
+      <c r="J35" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="12.85" customHeight="1" s="17">
       <c r="A36" s="18" t="inlineStr"/>
@@ -1956,6 +2114,11 @@
           <t>scratch_then_display_test</t>
         </is>
       </c>
+      <c r="J36" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="25.5" customHeight="1" s="17">
       <c r="A37" s="18" t="inlineStr"/>
@@ -1999,6 +2162,11 @@
       <c r="I37" s="18" t="inlineStr">
         <is>
           <t>random_regression_test</t>
+        </is>
+      </c>
+      <c r="J37" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
     </row>
@@ -2036,6 +2204,11 @@
       <c r="I38" s="18" t="inlineStr">
         <is>
           <t>virtual_seq_stress_test</t>
+        </is>
+      </c>
+      <c r="J38" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -2075,6 +2248,11 @@
           <t>enable_off_overflow_test</t>
         </is>
       </c>
+      <c r="J39" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="18" t="inlineStr"/>
@@ -2106,6 +2284,11 @@
       <c r="I40" s="18" t="inlineStr">
         <is>
           <t>poll_until_done_stress_test</t>
+        </is>
+      </c>
+      <c r="J40" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2549,7 @@
       </c>
       <c r="J5" s="18" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -2423,7 +2606,7 @@
       </c>
       <c r="J6" s="18" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="K6" s="18" t="inlineStr">
@@ -2480,7 +2663,7 @@
       </c>
       <c r="J7" s="18" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -2537,7 +2720,7 @@
       </c>
       <c r="J8" s="18" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="K8" s="18" t="inlineStr">
@@ -2594,7 +2777,7 @@
       </c>
       <c r="J9" s="18" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -2651,7 +2834,7 @@
       </c>
       <c r="J10" s="18" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="K10" s="18" t="inlineStr">
@@ -2936,7 +3119,7 @@
       </c>
       <c r="J15" s="18" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K15" s="18" t="inlineStr">
@@ -2993,7 +3176,7 @@
       </c>
       <c r="J16" s="18" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="K16" s="18" t="inlineStr">
@@ -3050,7 +3233,7 @@
       </c>
       <c r="J17" s="18" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="K17" s="18" t="inlineStr">
@@ -3206,7 +3389,7 @@
       </c>
       <c r="G20" s="18" t="inlineStr">
         <is>
-          <t>1. Drive error_q=74565. 2. Hold &gt;=1002 cycles. 3. Monitor samples sel_out one-hot</t>
+          <t>1. Drive error_q=74565. 2. Hold &gt;=1002 cycles. 3. Collect 6+ sel_out samples</t>
         </is>
       </c>
       <c r="H20" s="18" t="inlineStr">
@@ -3278,7 +3461,7 @@
       </c>
       <c r="J21" s="18" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="K21" s="18" t="inlineStr">
@@ -3506,7 +3689,7 @@
       </c>
       <c r="J25" s="18" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="K25" s="18" t="inlineStr">
@@ -3563,7 +3746,7 @@
       </c>
       <c r="J26" s="18" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="K26" s="18" t="inlineStr">
@@ -3620,7 +3803,7 @@
       </c>
       <c r="J27" s="18" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="K27" s="18" t="inlineStr">
@@ -3677,7 +3860,7 @@
       </c>
       <c r="J28" s="18" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K28" s="18" t="inlineStr">
@@ -3962,7 +4145,7 @@
       </c>
       <c r="J33" s="18" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="K33" s="18" t="inlineStr">
@@ -4133,7 +4316,7 @@
       </c>
       <c r="J36" s="18" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="K36" s="18" t="inlineStr">
@@ -4190,7 +4373,7 @@
       </c>
       <c r="J37" s="18" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K37" s="18" t="inlineStr">

--- a/LED_MUX_CONTROLLER_testplan.xlsx
+++ b/LED_MUX_CONTROLLER_testplan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TestPlan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TestPlan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -690,7 +690,7 @@
 3) Read 0x4004 expect Done=0.
 4) Read 0x4008 expect 0.
 Constraints: No APB traffic during reset assert.
-Checkers: SCB-1, SCB-2, SCB-3; assert_sel_out_reset_value, assert_seg_out_reset_value.</t>
+Checkers: SCB-1, SCB-2, SCB-3; assert_sel_out_reset_value, assert_seg_out_reset_value; COV cg_enable.default_at_reset, cg_done.bin_0.</t>
         </is>
       </c>
       <c r="F4" s="18" t="inlineStr">
@@ -698,7 +698,11 @@
           <t>assert_sel_out_reset_value, assert_seg_out_reset_value</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr"/>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>cg_enable, cg_done</t>
+        </is>
+      </c>
       <c r="H4" s="18" t="inlineStr">
         <is>
           <t>line, branch</t>
@@ -735,7 +739,7 @@
 3) Write 0x4000=1.
 4) Read 0x4000.
 Constraints: wdata[0] only (FR 3.4, §4.3).
-Checkers: SCB-1; COV cg_enable.</t>
+Checkers: SCB-1; COV cg_enable (cp_led_enable, cp_enable_trans).</t>
         </is>
       </c>
       <c r="F5" s="18" t="inlineStr"/>
@@ -1293,7 +1297,7 @@
 3) Poll Done.
 4) Scoreboard compare digits 0,0,0,0,4,2.
 Constraints: error_q==42; C-4 hold, C-5 latency (AC-B1).
-Checkers: SCB-4, SCB-5, SCB-6, SCB-8; assert_sel_out_onehot_active_low, assert_seg_out_bit7_always_one, check_60_80_cycle; COV cg_digits, cg_error_q.</t>
+Checkers: SCB-4, SCB-5, SCB-6, SCB-8; assert_sel_out_onehot_active_low, assert_seg_out_bit7_always_one, check_60_80_cycle; COV cg_error_q, cg_digits (cp_digit_pos, cp_digit_val).</t>
         </is>
       </c>
       <c r="F18" s="18" t="inlineStr">
@@ -1303,7 +1307,7 @@
       </c>
       <c r="G18" s="18" t="inlineStr">
         <is>
-          <t>cg_digits, cg_error_q</t>
+          <t>cg_error_q, cg_digits</t>
         </is>
       </c>
       <c r="H18" s="18" t="inlineStr">
@@ -1573,7 +1577,7 @@
 2) Poll Done.
 3) Expect display 000001.
 Constraints: Golden = error_q % 1_000_000 (FR 3.6, C-3, AC-B4).
-Checkers: SCB-9; assert_sel_out_onehot_active_low, assert_seg_out_bit7_always_one; COV cg_overflow, cg_digits.</t>
+Checkers: SCB-9; assert_sel_out_onehot_active_low, assert_seg_out_bit7_always_one; COV cg_overflow, cg_error_q overflow bins.</t>
         </is>
       </c>
       <c r="F24" s="18" t="inlineStr">
@@ -1583,7 +1587,7 @@
       </c>
       <c r="G24" s="18" t="inlineStr">
         <is>
-          <t>cg_overflow, cg_digits</t>
+          <t>cg_overflow, cg_error_q</t>
         </is>
       </c>
       <c r="H24" s="18" t="inlineStr">
@@ -1707,7 +1711,7 @@
 2) Drive error_q=55.
 3) Confirm seg_out does not update.
 Constraints: LED_enable==0 (FR 3.4, AC-E2).
-Checkers: SCB-7; COV cg_enable.</t>
+Checkers: SCB-7; COV cg_enable (bin_off, on_to_off).</t>
         </is>
       </c>
       <c r="F27" s="18" t="inlineStr"/>
@@ -1955,7 +1959,7 @@
         <is>
           <t>1) For d in 0..9: drive error_q with ones digit d; poll Done; compare encoding.
 Constraints: 10 iterations (AC-C1, AC-B1).
-Checkers: SCB-5; cover_seg_out_decimal_digit; COV cg_digits.</t>
+Checkers: SCB-5; cover_seg_out_decimal_digit; COV cg_digits, cx_digit_pos_x_digit_val.</t>
         </is>
       </c>
       <c r="F33" s="18" t="inlineStr">
@@ -1965,7 +1969,7 @@
       </c>
       <c r="G33" s="18" t="inlineStr">
         <is>
-          <t>cg_digits</t>
+          <t>cg_digits, cx_digit_pos_x_digit_val</t>
         </is>
       </c>
       <c r="H33" s="18" t="inlineStr">
@@ -2009,7 +2013,7 @@
 4) Poll Done.
 5) Scoreboard pass.
 Constraints: error_q=42.
-Checkers: SCB-1..9; assert_sel_out_reset_value, assert_seg_out_reset_value, assert_sel_out_onehot_active_low, assert_seg_out_bit7_always_one, assert_apb_setup_phase, assert_apb_access_phase, assert_apb_pready_complete, assert_apb_pslerr_invalid_addr, cover_sel_out_digit_position, cover_seg_out_decimal_digit, check_60_80_cycle, check_hold_1002_cycle; COV all.</t>
+Checkers: SCB-1..9; assert_sel_out_reset_value, assert_seg_out_reset_value, assert_sel_out_onehot_active_low, assert_seg_out_bit7_always_one, assert_apb_setup_phase, assert_apb_access_phase, assert_apb_pready_complete, assert_apb_pslerr_invalid_addr, cover_sel_out_digit_position, cover_seg_out_decimal_digit, check_60_80_cycle, check_hold_1002_cycle; COV cg_enable, cg_done, cg_error_q, cg_digits, cg_overflow.</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
@@ -2019,7 +2023,7 @@
       </c>
       <c r="G34" s="18" t="inlineStr">
         <is>
-          <t>cg_error_q, cg_digits, cg_enable, cg_done, cg_overflow</t>
+          <t>cg_enable, cg_done, cg_error_q, cg_digits, cg_overflow</t>
         </is>
       </c>
       <c r="H34" s="18" t="inlineStr">
